--- a/data/trans_camb/P1416-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1416-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,17</t>
+          <t>5,72</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,11</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>2,68</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 3,8</t>
+          <t>-2,95; 4,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 5,96</t>
+          <t>-1,95; 5,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 16,43</t>
+          <t>0,18; 12,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 2,02</t>
+          <t>-6,24; 1,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 2,33</t>
+          <t>-5,62; 2,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 4,46</t>
+          <t>-5,64; 5,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 1,23</t>
+          <t>-3,77; 1,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,84</t>
+          <t>-2,68; 2,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 9,28</t>
+          <t>-1,12; 6,99</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-9,77%</t>
+          <t>-5,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,95; 57,65</t>
+          <t>-31,39; 67,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 87,02</t>
+          <t>-19,84; 85,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,81; 225,69</t>
+          <t>1,43; 175,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,45; 23,31</t>
+          <t>-47,38; 12,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 23,66</t>
+          <t>-42,76; 25,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,31; 47,33</t>
+          <t>-43,8; 57,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,15; 14,52</t>
+          <t>-33,81; 17,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 33,73</t>
+          <t>-23,93; 34,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 107,25</t>
+          <t>-10,6; 82,17</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>2,66</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,39</t>
+          <t>2,84</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,92</t>
+          <t>-4,58; 1,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 1,03</t>
+          <t>-4,35; 1,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 8,07</t>
+          <t>-1,04; 7,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 1,23</t>
+          <t>-5,6; 1,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 2,55</t>
+          <t>-4,37; 2,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 5,2</t>
+          <t>-1,31; 6,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,2</t>
+          <t>-4,04; 0,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,97</t>
+          <t>-3,6; 0,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 5,31</t>
+          <t>0,34; 5,84</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 15,91</t>
+          <t>-46,74; 19,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,62; 15,73</t>
+          <t>-46,06; 19,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 121,45</t>
+          <t>-13,44; 98,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,46; 14,03</t>
+          <t>-44,5; 13,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 29,91</t>
+          <t>-35,16; 30,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,47; 56,07</t>
+          <t>-11,08; 74,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,1; 2,37</t>
+          <t>-38,76; 2,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,57; 12,58</t>
+          <t>-35,58; 11,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 64,11</t>
+          <t>3,27; 70,74</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>4,62</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>2,64</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,3</t>
+          <t>-3,16; 2,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 0,84</t>
+          <t>-4,23; 0,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 8,68</t>
+          <t>1,33; 8,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 3,21</t>
+          <t>-3,66; 3,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 2,67</t>
+          <t>-4,21; 2,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,81</t>
+          <t>-2,52; 3,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,76</t>
+          <t>-2,71; 1,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,79</t>
+          <t>-3,76; 0,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,17</t>
+          <t>0,25; 4,87</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,27; 47,2</t>
+          <t>-38,84; 49,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 19,32</t>
+          <t>-54,07; 15,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,04; 166,82</t>
+          <t>16,43; 161,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,74; 34,79</t>
+          <t>-29,1; 36,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 30,21</t>
+          <t>-34,0; 27,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,73; 43,7</t>
+          <t>-19,9; 44,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,02; 23,07</t>
+          <t>-27,62; 21,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,99; 10,58</t>
+          <t>-38,18; 10,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,7; 66,0</t>
+          <t>2,44; 63,8</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,88</t>
+          <t>5,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,73; -0,65</t>
+          <t>-5,85; -0,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 0,46</t>
+          <t>-4,61; 0,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 6,6</t>
+          <t>1,93; 8,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,67; -0,7</t>
+          <t>-7,13; -0,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 1,24</t>
+          <t>-5,83; 1,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,78</t>
+          <t>1,49; 8,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,55; -1,15</t>
+          <t>-5,68; -1,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,27</t>
+          <t>-4,27; -0,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 5,79</t>
+          <t>2,56; 7,35</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>68,01%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-77,78; -11,82</t>
+          <t>-78,43; -9,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-66,44; 13,77</t>
+          <t>-67,02; 17,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,15; 140,52</t>
+          <t>22,69; 216,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-61,49; -5,19</t>
+          <t>-60,25; -5,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,53; 16,45</t>
+          <t>-47,67; 16,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,46; 100,63</t>
+          <t>12,62; 103,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-61,42; -17,8</t>
+          <t>-61,98; -21,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,61; 4,32</t>
+          <t>-47,64; -1,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 83,76</t>
+          <t>27,02; 115,23</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,81</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>3,3</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,03; -0,08</t>
+          <t>-6,31; -0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 0,61</t>
+          <t>-5,75; 0,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 4,42</t>
+          <t>-2,03; 4,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 0,32</t>
+          <t>-6,18; 0,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 4,61</t>
+          <t>-2,84; 4,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 8,06</t>
+          <t>1,24; 7,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,33; -0,76</t>
+          <t>-5,4; -0,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 1,56</t>
+          <t>-3,69; 1,39</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,24</t>
+          <t>0,8; 5,42</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>48,05%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-72,38; 0,66</t>
+          <t>-74,09; 5,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-68,23; 16,96</t>
+          <t>-67,95; 9,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 96,39</t>
+          <t>-23,55; 107,34</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-67,59; 7,01</t>
+          <t>-66,61; 10,27</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,87; 84,28</t>
+          <t>-30,95; 82,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,74; 156,82</t>
+          <t>10,91; 150,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-62,14; -11,49</t>
+          <t>-65,47; -15,18</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-39,21; 28,55</t>
+          <t>-43,0; 24,71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8,41; 96,22</t>
+          <t>9,49; 99,24</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,35</t>
+          <t>0,46</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-1,31</t>
+          <t>0,68</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 2,84</t>
+          <t>-4,01; 3,07</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,69; -0,83</t>
+          <t>-6,33; -1,05</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 4,18</t>
+          <t>-2,0; 4,16</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,27; -2,1</t>
+          <t>-9,61; -2,32</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,68; -2,85</t>
+          <t>-10,25; -2,92</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 0,86</t>
+          <t>-3,82; 3,88</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,88; -0,73</t>
+          <t>-6,05; -0,84</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,46; -2,69</t>
+          <t>-7,4; -2,76</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 1,45</t>
+          <t>-1,88; 3,03</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-33,92%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-17,55%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-66,11; 97,66</t>
+          <t>-68,3; 99,84</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-92,4; -14,67</t>
+          <t>-92,64; -22,69</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-35,11; 148,2</t>
+          <t>-32,68; 144,74</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-77,45; -27,02</t>
+          <t>-78,39; -25,12</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-79,97; -32,34</t>
+          <t>-82,03; -32,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-74,74; 11,13</t>
+          <t>-30,39; 51,65</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-65,62; -10,83</t>
+          <t>-66,77; -10,55</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-80,72; -43,39</t>
+          <t>-80,96; -43,8</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-58,87; 21,82</t>
+          <t>-22,05; 51,78</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,23</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,78</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,84</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 3,43</t>
+          <t>-4,35; 3,1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,99</t>
+          <t>-4,64; 2,28</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 3,97</t>
+          <t>-2,56; 4,13</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 4,37</t>
+          <t>-2,56; 4,3</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 3,74</t>
+          <t>-2,98; 3,76</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,33; 6,79</t>
+          <t>0,72; 6,75</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,75</t>
+          <t>-2,28; 2,96</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,37</t>
+          <t>-2,51; 2,28</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,18; 4,88</t>
+          <t>0,58; 5,13</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>65,33%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-71,53; 146,98</t>
+          <t>-73,31; 147,54</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-69,24; 117,27</t>
+          <t>-73,28; 100,0</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-38,17; 174,03</t>
+          <t>-39,71; 175,78</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-40,25; 153,34</t>
+          <t>-41,19; 161,32</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-50,39; 127,7</t>
+          <t>-49,67; 137,08</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,62; 233,83</t>
+          <t>6,68; 258,74</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-42,34; 93,21</t>
+          <t>-40,98; 96,95</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-44,71; 73,16</t>
+          <t>-45,34; 72,79</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 159,02</t>
+          <t>7,09; 179,96</t>
         </is>
       </c>
     </row>
@@ -2146,37 +2146,37 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>3,03</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>-2,27</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>-1,65</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2,39</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-1,92</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-1,69</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
           <t>2,72</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-2,27</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-1,65</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-1,92</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-1,69</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,43</t>
+          <t>-2,8; -0,36</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,95; -0,56</t>
+          <t>-2,94; -0,72</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,45</t>
+          <t>1,52; 4,48</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,58; -0,89</t>
+          <t>-3,55; -0,92</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,11; -0,4</t>
+          <t>-3,1; -0,32</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,72</t>
+          <t>1,01; 3,85</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,73; -0,93</t>
+          <t>-2,83; -1,07</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,66</t>
+          <t>-2,6; -0,81</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,21</t>
+          <t>1,71; 3,69</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-38,12; -7,04</t>
+          <t>-38,15; -5,65</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-40,28; -8,06</t>
+          <t>-39,98; -11,15</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7,23; 72,31</t>
+          <t>21,28; 72,59</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-34,97; -9,92</t>
+          <t>-34,62; -10,31</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-29,87; -4,33</t>
+          <t>-29,98; -4,1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 30,11</t>
+          <t>9,45; 42,68</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-31,61; -12,32</t>
+          <t>-32,55; -13,24</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-29,92; -8,68</t>
+          <t>-30,16; -10,05</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6,71; 41,67</t>
+          <t>19,52; 47,47</t>
         </is>
       </c>
     </row>
